--- a/LICOR_Calibration/UofU_LiCOR200R.xlsx
+++ b/LICOR_Calibration/UofU_LiCOR200R.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tomw/Documents/VBUS/LEMSv3/Codes/LICOR_Calibration/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tomw/Documents/VBUS/VBUS-Albedo-Measurements/LICOR_Calibration/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19552F93-BF6A-D148-BA7E-A5585B2C00FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92806C30-F77E-8446-A1D1-E11F0EDA18DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -938,7 +938,7 @@
         <v>7.4219999999999999E-8</v>
       </c>
       <c r="D2" s="22">
-        <f t="shared" ref="D2:D62" si="1">($J$4-$J$5)/(C2*$J$3)</f>
+        <f t="shared" ref="D2:D42" si="1">($J$4-$J$5)/(C2*$J$3)</f>
         <v>33683.64322285098</v>
       </c>
       <c r="E2">
@@ -946,7 +946,7 @@
         <v>2.9999999999999996</v>
       </c>
       <c r="G2">
-        <f t="shared" ref="G2:G21" si="3">(C2*$J$3)*F2</f>
+        <f t="shared" ref="G2:G42" si="3">(C2*$J$3)*F2</f>
         <v>0</v>
       </c>
       <c r="I2" s="41" t="s">
@@ -1489,6 +1489,10 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
+      <c r="G22">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
@@ -1509,6 +1513,10 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
+      <c r="G23">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
@@ -1529,6 +1537,10 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
+      <c r="G24">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
@@ -1549,6 +1561,10 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
+      <c r="G25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
@@ -1569,6 +1585,10 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
+      <c r="G26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
@@ -1589,6 +1609,10 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
+      <c r="G27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
@@ -1609,6 +1633,10 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
+      <c r="G28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
@@ -1629,6 +1657,10 @@
         <f t="shared" si="2"/>
         <v>2.9999999999999996</v>
       </c>
+      <c r="G29">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
@@ -1649,6 +1681,10 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
+      <c r="G30">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
@@ -1669,6 +1705,10 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
+      <c r="G31">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
@@ -1689,8 +1729,12 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G32">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>38</v>
       </c>
@@ -1709,8 +1753,12 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G33">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -1729,8 +1777,12 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>37</v>
       </c>
@@ -1749,8 +1801,12 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G35">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>33</v>
       </c>
@@ -1769,8 +1825,12 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G36">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>40</v>
       </c>
@@ -1789,8 +1849,12 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G37">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>23</v>
       </c>
@@ -1809,8 +1873,12 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G38">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>34</v>
       </c>
@@ -1829,8 +1897,12 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G39">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>19</v>
       </c>
@@ -1849,8 +1921,12 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G40">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>41</v>
       </c>
@@ -1869,8 +1945,12 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>42</v>
       </c>
@@ -1889,23 +1969,27 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G42">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D43" s="22"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D44" s="22"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D45" s="22"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D46" s="22"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D47" s="22"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D48" s="22"/>
     </row>
     <row r="49" spans="4:4" x14ac:dyDescent="0.2">
